--- a/outputs/Block2_2026_Fold_Forecasts_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Forecasts_v12.xlsx
@@ -486,25 +486,25 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>50.99509392265193</v>
+        <v>52.13255079006773</v>
       </c>
       <c r="G2">
-        <v>46.20490607734807</v>
+        <v>45.06744920993228</v>
       </c>
       <c r="H2">
-        <v>4.790187845303862</v>
+        <v>7.065101580135458</v>
       </c>
       <c r="I2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="J2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -524,25 +524,25 @@
         <v>18</v>
       </c>
       <c r="F3">
-        <v>50.99509392265193</v>
+        <v>52.13255079006773</v>
       </c>
       <c r="G3">
-        <v>46.20490607734807</v>
+        <v>45.06744920993228</v>
       </c>
       <c r="H3">
-        <v>4.790187845303867</v>
+        <v>7.065101580135447</v>
       </c>
       <c r="I3">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J3">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -562,25 +562,25 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>50.98197790055249</v>
+        <v>52.11914221218962</v>
       </c>
       <c r="G4">
-        <v>46.19302209944752</v>
+        <v>45.05585778781037</v>
       </c>
       <c r="H4">
-        <v>4.788955801104971</v>
+        <v>7.063284424379241</v>
       </c>
       <c r="I4">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J4">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L4">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -600,25 +600,25 @@
         <v>18</v>
       </c>
       <c r="F5">
-        <v>50.78523756906078</v>
+        <v>51.91801354401807</v>
       </c>
       <c r="G5">
-        <v>46.01476243093924</v>
+        <v>44.88198645598194</v>
       </c>
       <c r="H5">
-        <v>4.770475138121549</v>
+        <v>7.036027088036134</v>
       </c>
       <c r="I5">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J5">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -638,25 +638,25 @@
         <v>18</v>
       </c>
       <c r="F6">
-        <v>50.9032817679558</v>
+        <v>52.038690744921</v>
       </c>
       <c r="G6">
-        <v>46.1217182320442</v>
+        <v>44.98630925507901</v>
       </c>
       <c r="H6">
-        <v>4.781563535911598</v>
+        <v>7.052381489841997</v>
       </c>
       <c r="I6">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="J6">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
